--- a/artifacts/reports/testcases/TC-UAT-WEB-01_VoIPWeb受入テストケース/TC-UAT-WEB-01_VoIPWeb受入テストケース.xlsx
+++ b/artifacts/reports/testcases/TC-UAT-WEB-01_VoIPWeb受入テストケース/TC-UAT-WEB-01_VoIPWeb受入テストケース.xlsx
@@ -2078,7 +2078,7 @@
       <c r="AD1" s="30" t="n"/>
       <c r="AE1" s="32" t="inlineStr">
         <is>
-          <t>種別</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="AF1" s="29" t="n"/>
@@ -2090,7 +2090,7 @@
       <c r="AL1" s="30" t="n"/>
       <c r="AM1" s="32" t="inlineStr">
         <is>
-          <t>第1回（DEV）</t>
+          <t>第1回（ローカル）</t>
         </is>
       </c>
       <c r="AN1" s="29" t="n"/>
@@ -2106,7 +2106,7 @@
       <c r="AX1" s="30" t="n"/>
       <c r="AY1" s="33" t="inlineStr">
         <is>
-          <t>第2回（PRD）</t>
+          <t>第2回（ローカル）</t>
         </is>
       </c>
       <c r="AZ1" s="29" t="n"/>
@@ -2455,7 +2455,7 @@
       <c r="AF5" s="27" t="n"/>
       <c r="AG5" s="32" t="inlineStr">
         <is>
-          <t>テスト結果 - 第1回（DEV）</t>
+          <t>テスト結果 - 第1回</t>
         </is>
       </c>
       <c r="AH5" s="29" t="n"/>
@@ -2473,7 +2473,7 @@
       <c r="AT5" s="30" t="n"/>
       <c r="AU5" s="32" t="inlineStr">
         <is>
-          <t>テスト結果 - 第2回（PRD）</t>
+          <t>テスト結果 - 第2回</t>
         </is>
       </c>
       <c r="AV5" s="29" t="n"/>
@@ -5099,7 +5099,7 @@
       <c r="BJ31" s="5" t="n"/>
       <c r="BK31" s="40" t="n"/>
     </row>
-    <row r="32" ht="45" customHeight="1">
+    <row r="32" ht="105" customHeight="1">
       <c r="A32" s="63" t="inlineStr">
         <is>
           <t>UAT-WEB-026</t>
@@ -5140,7 +5140,9 @@
       <c r="R32" s="64" t="inlineStr">
         <is>
           <t>① 対象テナントのチェックボックスを選択する
-② 「ログイン情報通知」をクリックする</t>
+② 「ログイン情報通知」をクリックする
+③ 「メール送信の確認」ポップアップで「OK」ボタンをクリックする
+④ 「ログイン情報送信確認」ポップアップで「キャンセル」ボタンをクリックする</t>
         </is>
       </c>
       <c r="S32" s="5" t="n"/>
